--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3148,57 +3148,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129745963</v>
+        <v>136669688</v>
       </c>
       <c r="B26" t="n">
-        <v>56925</v>
+        <v>75564</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100045</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gesebol 2:2, Vg</t>
+          <t>Mjögasjön, Mjögasjön, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>362701</v>
+        <v>362873</v>
       </c>
       <c r="R26" t="n">
-        <v>6401152</v>
+        <v>6401200</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3225,22 +3213,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spridda fynd på flertal gammelgranar utmed fuktstråket</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3255,27 +3248,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Boel Nilsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Boel Nilsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129745963</t>
+          <t>https://artportalen.se/Sighting/136669688</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129745850</v>
+        <v>129745963</v>
       </c>
       <c r="B27" t="n">
-        <v>57141</v>
+        <v>56925</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3283,37 +3276,33 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100045</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3358,7 +3347,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3368,7 +3357,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3394,16 +3383,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129745850</t>
+          <t>https://artportalen.se/Sighting/129745963</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129671481</v>
+        <v>129745850</v>
       </c>
       <c r="B28" t="n">
-        <v>97983</v>
+        <v>57141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3411,37 +3400,53 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gesebol, Vg</t>
+          <t>Gesebol 2:2, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>362639</v>
+        <v>362701</v>
       </c>
       <c r="R28" t="n">
-        <v>6401070</v>
+        <v>6401152</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3465,12 +3470,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3485,16 +3500,118 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745850</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129671481</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gesebol, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>362639</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6401070</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129671481</t>
         </is>
@@ -3529,6 +3646,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>136669688</v>
       </c>
       <c r="B26" t="n">
-        <v>75564</v>
+        <v>75566</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>136669688</v>
       </c>
       <c r="B26" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 52087-2025 artfynd.xlsx
+++ b/artfynd/A 52087-2025 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>136669688</v>
       </c>
       <c r="B26" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
